--- a/mosip_master/xlsx/language.xlsx
+++ b/mosip_master/xlsx/language.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M1074108\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4F197C-A0B3-4E06-A7CD-3986704E8F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563D241E-6BBA-4EF4-9D52-8B9A7D13E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9420" yWindow="5050" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>code</t>
   </si>
@@ -52,66 +52,6 @@
   </si>
   <si>
     <t>TRUE</t>
-  </si>
-  <si>
-    <t>fra</t>
-  </si>
-  <si>
-    <t>French</t>
-  </si>
-  <si>
-    <t>français</t>
-  </si>
-  <si>
-    <t>ara</t>
-  </si>
-  <si>
-    <t>Arabic</t>
-  </si>
-  <si>
-    <t>الهندو أوروبية</t>
-  </si>
-  <si>
-    <t>kan</t>
-  </si>
-  <si>
-    <t>ಕನ್ನಡ</t>
-  </si>
-  <si>
-    <t>ಇಂಡೋ-ಯುರೋಪಿಯನ್</t>
-  </si>
-  <si>
-    <t>Kannada</t>
-  </si>
-  <si>
-    <t>hin</t>
-  </si>
-  <si>
-    <t>हिन्दी</t>
-  </si>
-  <si>
-    <t>भारोपीय</t>
-  </si>
-  <si>
-    <t>Hindi</t>
-  </si>
-  <si>
-    <t>tam</t>
-  </si>
-  <si>
-    <t>தமிழ்</t>
-  </si>
-  <si>
-    <t>இந்தோ-ஐரோப்பிய</t>
-  </si>
-  <si>
-    <t>Tamil</t>
-  </si>
-  <si>
-    <t>spa</t>
-  </si>
-  <si>
-    <t>Spanish</t>
   </si>
 </sst>
 </file>
@@ -195,9 +135,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -235,7 +175,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -341,7 +281,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -483,7 +423,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -491,13 +431,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="5" max="5" width="8.42578125" style="1"/>
+    <col min="5" max="5" width="8.453125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -514,7 +454,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -528,108 +468,6 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/mosip_master/xlsx/language.xlsx
+++ b/mosip_master/xlsx/language.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BarnabyTwyford\repos\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\M1074108\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563D241E-6BBA-4EF4-9D52-8B9A7D13E0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4F197C-A0B3-4E06-A7CD-3986704E8F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9420" yWindow="5050" windowWidth="22070" windowHeight="13070" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>code</t>
   </si>
@@ -52,6 +52,66 @@
   </si>
   <si>
     <t>TRUE</t>
+  </si>
+  <si>
+    <t>fra</t>
+  </si>
+  <si>
+    <t>French</t>
+  </si>
+  <si>
+    <t>français</t>
+  </si>
+  <si>
+    <t>ara</t>
+  </si>
+  <si>
+    <t>Arabic</t>
+  </si>
+  <si>
+    <t>الهندو أوروبية</t>
+  </si>
+  <si>
+    <t>kan</t>
+  </si>
+  <si>
+    <t>ಕನ್ನಡ</t>
+  </si>
+  <si>
+    <t>ಇಂಡೋ-ಯುರೋಪಿಯನ್</t>
+  </si>
+  <si>
+    <t>Kannada</t>
+  </si>
+  <si>
+    <t>hin</t>
+  </si>
+  <si>
+    <t>हिन्दी</t>
+  </si>
+  <si>
+    <t>भारोपीय</t>
+  </si>
+  <si>
+    <t>Hindi</t>
+  </si>
+  <si>
+    <t>tam</t>
+  </si>
+  <si>
+    <t>தமிழ்</t>
+  </si>
+  <si>
+    <t>இந்தோ-ஐரோப்பிய</t>
+  </si>
+  <si>
+    <t>Tamil</t>
+  </si>
+  <si>
+    <t>spa</t>
+  </si>
+  <si>
+    <t>Spanish</t>
   </si>
 </sst>
 </file>
@@ -135,9 +195,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,7 +235,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -281,7 +341,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,7 +483,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -431,13 +491,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="8.453125" style="1"/>
+    <col min="5" max="5" width="8.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -454,7 +514,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -468,6 +528,108 @@
         <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
